--- a/운영원장/수사해당가든_운영원장.xlsx
+++ b/운영원장/수사해당가든_운영원장.xlsx
@@ -10,14 +10,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재고" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="거래" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협력농가" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="교육" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="견적서" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="거래처" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자재" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="교육" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="견적서" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'재고'!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'거래'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'거래'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'거래처'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'자재'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,14 +55,14 @@
     </font>
     <font>
       <name val="Malgun Gothic"/>
-      <color rgb="0038463E"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00226B3A"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Malgun Gothic"/>
-      <b val="1"/>
-      <color rgb="00226B3A"/>
-      <sz val="12"/>
+      <color rgb="0038463E"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Malgun Gothic"/>
@@ -186,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -195,39 +198,39 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -246,7 +249,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -299,6 +302,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,11 +675,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="98" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -683,152 +692,154 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>재고 · 매입/매출 · 협력농가 · 교육을 한 파일에서 관리하는 단일 원장입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>재고 · 거래(매입/매출) · 거래처 · 자재 · 교육을 한 파일에서 관리하는 단일 원장입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>● 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>① 재고 — 나무를 등록하는 핵심 시트. 대형목은 1주=1행(개체), 묘목은 규격묶음+수량(로트).</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>① 재고 — 나무 등록(핵심). 대형목=1주 1행(개체), 묘목=규격묶음+수량(로트).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>② 거래 — 매입·매출을 한 표에 기록. 여기 쌓인 데이터가 대시보드로 자동 집계됩니다.</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>② 거래 — 매입·매출을 한 표에 기록(나무+자재 모두). 대시보드로 자동 집계.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>③ 협력농가 — 우리가 위탁·매입해 파는 협력 농가 목록.</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>③ 거래처 — 고객·협력농가·자재매입처 등 모든 거래 상대 정보 DB.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>④ 교육 — 교육 회차·인원·시간 기록. 홈페이지 '누적 교육 인원'과 연동 예정.</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>④ 자재 — 농약·비료·상토·원예자재의 '재고 수량' 관리(나무와 별도).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>⑤ 대시보드 — 재고 현황·기간별 매출/매입/마진·교육 누계가 자동 계산됩니다.</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>⑤ 교육 — 교육 회차·인원·시간(홈페이지 '누적 교육 인원' 연동 예정).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>⑥ 견적서 — 품목만 채우면 합계가 자동 계산되는 견적서 양식(인쇄/PDF용).</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>⑥ 대시보드 — 재고 현황·기간별 매출/매입/마진·교육 누계 자동 계산.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>● 사용법</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>⑦ 견적서 — 품목+계약사항을 채우면 합계 자동 계산(인쇄/PDF용).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>1. 이 엑셀 파일을 구글 드라이브에 끌어다 놓으면 구글시트로 열립니다. (또는 엑셀로 바로 사용)</t>
+          <t>● 관리 방식: 개체 vs 로트</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2. 재고·거래·교육 시트에 데이터를 계속 추가하세요. 대시보드는 자동으로 갱신됩니다.</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>· 개체 = 나무 1그루를 1줄로 개별 관리(대형목처럼 한 그루가 비쌀 때).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>3. 노란색 칸(대시보드 '기준연도')만 상황에 맞게 바꾸면 기간별 집계가 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>· 로트 = 같은 규격을 '묶음+수량'으로 관리(묘목처럼 수백 주일 때).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>● 나무 재고의 원칙 (중요)</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>● 자재(농약·비료·원예자재) 처리</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>· 년생으로 규격을 추정하지 않고, R(목대)·수고·지하고를 '실측값'으로 직접 적습니다.</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>· 구입(돈 나감) → '거래' 시트에 매입으로 입력(품목분류=자재·경비). 회계에 반영됨.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>· 나무는 자라므로 봄·가을 등 정기적으로 규격과 '최근실측일'을 갱신하세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>· '소유구분'에 자가/협력농가를 구분하면, 협력농가 나무 판매 시 마진 계산의 기초가 됩니다.</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>· 남은 수량 → '자재' 시트에서 관리. 나무 재고(재고 시트)와 성격이 달라 분리합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>● 나무 재고 원칙</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>● 세금계산서 관련 확인 필요</t>
+          <t>· 년생으로 규격 추정 금지 → R(목대)·수고·지하고를 '실측값'으로 적기.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>· 묘목·화훼 등 미가공 농산물은 부가세 '면세'일 수 있어, 세금계산서가 아니라 '계산서'를 발행합니다.</t>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>· 나무는 자라므로 봄·가을 등 정기적으로 규격과 '최근실측일' 갱신.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>· 원예자재·식재 시공은 과세일 수 있어 겸업이 됩니다. 정확한 구분은 세무사 확인을 권장합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>· 계산서 발행은 국세청 홈택스(무료·공인)를 이용하세요. 견적서는 이 파일의 '견적서' 시트로 만듭니다.</t>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>· '소유구분(자가/협력농가)'을 채우면 협력농가 나무 판매 시 마진 계산의 기초가 됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>● 세금계산서 (확인 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>· 묘목 등 미가공 농산물은 부가세 '면세'일 수 있어 세금계산서 대신 '계산서'를 발행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>· 원예자재·식재 시공은 과세일 수 있어 겸업 → 세무사 확인 권장. 발행은 홈택스(무료).</t>
         </is>
       </c>
     </row>
@@ -1518,21 +1529,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1548,50 +1560,55 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>품목분류</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>관리번호</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>품목명</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>단가(원)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>금액(원)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>거래처</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>결제상태</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>계산서</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1608,45 +1625,50 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
+          <t>나무</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
           <t>SH-2026-003</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>수사해당화 R9 정원목</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="G2" s="8" t="n">
         <v>180000</v>
       </c>
-      <c r="G2" s="8">
-        <f>E2*F2</f>
-        <v/>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="8">
+        <f>F2*G2</f>
+        <v/>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>김○○</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>전화</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>미발행</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>마당 식재</t>
         </is>
@@ -1663,45 +1685,50 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
+          <t>나무</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
           <t>SH-2026-004</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>수사해당화 R8 다간(예산농원)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="G3" s="8" t="n">
         <v>120000</v>
       </c>
-      <c r="G3" s="8">
-        <f>E3*F3</f>
-        <v/>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="8">
+        <f>F3*G3</f>
+        <v/>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>예산농원</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>현장</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>해당없음</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>위탁 매입</t>
         </is>
@@ -1709,113 +1736,119 @@
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
-        <v>46117</v>
+        <v>46086</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>매입</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>SH-2026-004</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>수사해당화 R8 다간</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G4" s="8">
-        <f>E4*F4</f>
-        <v/>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>이○○</t>
-        </is>
+          <t>자재·경비</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>상토·영양제 패키지</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H4" s="8">
+        <f>F4*G4</f>
+        <v/>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>스마트스토어</t>
+          <t>○○종합자재</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>미발행</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>식재용 자재</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>46124</v>
+        <v>46114</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>매입</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>SH-2026-005</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>수사해당화 R6 마당목</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>90000</v>
-      </c>
-      <c r="G5" s="8">
-        <f>E5*F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>박○○</t>
-        </is>
+          <t>자재·경비</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>살균제(농약)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H5" s="8">
+        <f>F5*G5</f>
+        <v/>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>홈페이지견적</t>
+          <t>○○종합자재</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>현장</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
           <t>미발행</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>방문 예정</t>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>병해충 방제</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>46144</v>
+        <v>46117</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
@@ -1824,114 +1857,243 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>SH-2026-101</t>
+          <t>나무</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>수사해당화 R5 다간 묘목</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G6" s="8">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>정○○</t>
-        </is>
+          <t>SH-2026-004</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>수사해당화 R8 다간</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H6" s="8">
+        <f>F6*G6</f>
+        <v/>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>이○○</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
+          <t>스마트스토어</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>미발행</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>나무</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SH-2026-005</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>수사해당화 R6 마당목</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H7" s="8">
+        <f>F7*G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>박○○</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>홈페이지견적</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>미발행</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>방문 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>나무</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SH-2026-101</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>수사해당화 R5 다간 묘목</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H8" s="8">
+        <f>F8*G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>정○○</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>미발행</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
         <v>46160</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>나무</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>SH-2026-003</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>수사해당화 R9 정원목</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>180000</v>
       </c>
-      <c r="G7" s="8">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H9" s="8">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>○○조경</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>전화</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>미발행</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>조경 납품</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:M1"/>
+  <dataValidations count="5">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매입,매출"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"나무,자재·경비"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"스마트스토어,전화,현장,홈페이지견적,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,대기,미수"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"발행,미발행,해당없음"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1942,137 +2104,270 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="008B9890"/>
+    <tabColor rgb="005C6B62"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>농가명</t>
+          <t>거래처명</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>대표·담당</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>지역</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>주요 수종·규격</t>
-        </is>
-      </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>정산방식</t>
+          <t>사업자등록번호</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>정산·비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>예산농원</t>
+          <t>김○○</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>박○○</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>010-0000-0000</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>충남 예산</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>수사해당화 R8~R12</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>위탁</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>대형목 중심</t>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>개인 · 정원 식재</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
+          <t>이○○</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>010-0000-0000</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>○○조경</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>010-0000-0000</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>조경업체 · 정기 납품</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>예산농원</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>협력농가</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>박○○</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>010-0000-0000</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>충남 예산</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>위탁 · R8~R12 대형목</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>○○농가</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>협력농가</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>김○○</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>010-0000-0000</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>충남 홍성</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>수사해당화 묘목·소형</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>매입</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>묘목 다량</t>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>매입 · 묘목 다량</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>자재매입처</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>041-000-0000</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>충남 예산</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>농약·비료·상토·지주대</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"위탁,매입"</formula1>
+    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"고객,협력농가,자재매입처,기타"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2083,6 +2378,286 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D99B32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>규격·용량</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>현재고</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>안전재고</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>최근구입일</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>매입처</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>상토·영양제 패키지</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>상토·영양제</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>46086</v>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>식재 활착용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>유기질 비료</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>비료</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>20kg</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>포</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>46086</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>살균제</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>농약</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>병</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>46114</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>희석 사용 · 안전보관</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>살충제</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>농약</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>병</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>46114</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>병해충 방제</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>지주대 세트</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>원예자재</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>46101</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>○○종합자재</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>판매도 가능</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"농약,비료,상토·영양제,원예자재,기타"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E2719A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2268,22 +2843,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F8F4E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F29"/>
+  <dimension ref="B2:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2296,7 +2871,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>재고·거래·교육 시트에 데이터를 넣으면 아래 숫자가 자동으로 갱신됩니다.</t>
+          <t>재고·거래·교육 시트에 데이터를 넣으면 아래 숫자가 자동 갱신됩니다.</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2944,7 @@
     <row r="11">
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>재고 평가액(희망가 기준)</t>
+          <t>재고 평가액(희망가)</t>
         </is>
       </c>
       <c r="C11" s="16">
@@ -2432,11 +3007,11 @@
         </is>
       </c>
       <c r="C17" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,1,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,3,31))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,1,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,3,31))</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,1,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,3,31))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,1,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,3,31))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -2451,11 +3026,11 @@
         </is>
       </c>
       <c r="C18" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,4,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,6,30))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,4,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,6,30))</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,4,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,6,30))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,4,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,6,30))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -2470,11 +3045,11 @@
         </is>
       </c>
       <c r="C19" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,7,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,9,30))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,7,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,9,30))</f>
         <v/>
       </c>
       <c r="D19" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,7,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,9,30))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,7,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,9,30))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -2489,11 +3064,11 @@
         </is>
       </c>
       <c r="C20" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,10,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,12,31))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매출",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,10,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,12,31))</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>SUMIFS('거래'!$G:$G,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,10,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,12,31))</f>
+        <f>SUMIFS('거래'!$H:$H,'거래'!$B:$B,"매입",'거래'!$A:$A,"&gt;="&amp;DATE($C$13,10,1),'거래'!$A:$A,"&lt;="&amp;DATE($C$13,12,31))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -2558,57 +3133,64 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="12" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>※ 매입에는 나무 원가와 자재·경비가 함께 집계됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>■ 교육 누계 (홈페이지 연동 대상)</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>누적 교육 회차</t>
-        </is>
-      </c>
-      <c r="C26" s="15">
-        <f>COUNT('교육'!$B:$B)</f>
-        <v/>
-      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>누적 교육 인원</t>
+          <t>누적 교육 회차</t>
         </is>
       </c>
       <c r="C27" s="15">
-        <f>SUM('교육'!$D:$D)</f>
+        <f>COUNT('교육'!$B:$B)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>누적 교육 시간(h)</t>
+          <t>누적 교육 인원</t>
         </is>
       </c>
       <c r="C28" s="15">
-        <f>SUM('교육'!$E:$E)</f>
+        <f>SUM('교육'!$D:$D)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="14" t="inlineStr">
         <is>
+          <t>누적 교육 시간(h)</t>
+        </is>
+      </c>
+      <c r="C29" s="15">
+        <f>SUM('교육'!$E:$E)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
           <t>평균 만족도</t>
         </is>
       </c>
-      <c r="C29" s="26">
+      <c r="C30" s="26">
         <f>IFERROR(ROUND(AVERAGE('교육'!$H:$H),1),"-")</f>
         <v/>
       </c>
@@ -2618,14 +3200,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FBE3ED"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F31"/>
+  <dimension ref="B2:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2634,7 +3216,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2934,30 +3516,94 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>※ 본 견적은 발행일로부터 15일간 유효합니다. 규격·수량·식재 조건에 따라 변동될 수 있습니다.</t>
-        </is>
-      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>■ 계약사항 / 특약</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>1. 배송비는 견적 금액에 포함되지 않으며, 구매자(수신인) 부담입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>2. 하차·식재(심기) 비용은 별도이며, 현장 조건에 따라 협의합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>3. 살아있는 나무의 특성상 단순 변심에 의한 반품·교환은 불가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>4. 본 견적서는 발행일로부터 15일간 유효합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>5. 결제 조건: 계약금 30% / 잔금은 출고(수령) 시. (협의 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. 기타 특약: </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>공급자 (인)</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>구매자 (인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>※ 면세/과세 구분 및 부가세는 세무사 확인 후 확정하세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="15">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
